--- a/Data/CardBattle_RuntimeCardData_IntCardType.xlsx
+++ b/Data/CardBattle_RuntimeCardData_IntCardType.xlsx
@@ -970,219 +970,341 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:cols>
-    <x:col min="1" max="1" width="14" customWidth="1"/>
-    <x:col min="2" max="2" width="18" customWidth="1"/>
-    <x:col min="3" max="3" width="45" customWidth="1"/>
-    <x:col min="4" max="4" width="22" customWidth="1"/>
-    <x:col min="5" max="5" width="55" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" t="str">
-        <x:v>cardTextKey</x:v>
-      </x:c>
-      <x:c r="B1" t="str">
-        <x:v>koreanName</x:v>
-      </x:c>
-      <x:c r="C1" t="str">
-        <x:v>koreanDescription</x:v>
-      </x:c>
-      <x:c r="D1" t="str">
-        <x:v>englishName</x:v>
-      </x:c>
-      <x:c r="E1" t="str">
-        <x:v>englishDescription</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="B2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="E2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B3" t="str">
-        <x:v>일반 병사</x:v>
-      </x:c>
-      <x:c r="C3" t="str">
-        <x:v>기본 능력치를 가진 표준 카드입니다.</x:v>
-      </x:c>
-      <x:c r="D3" t="str">
-        <x:v>Normal Soldier</x:v>
-      </x:c>
-      <x:c r="E3" t="str">
-        <x:v>A standard card with balanced stats.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B4" t="str">
-        <x:v>원거리 병사</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>후방에서 안정적으로 공격하는 카드입니다.</x:v>
-      </x:c>
-      <x:c r="D4" t="str">
-        <x:v>Ranged Soldier</x:v>
-      </x:c>
-      <x:c r="E4" t="str">
-        <x:v>A card that attacks reliably from the back line.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B5" t="str">
-        <x:v>무쌍 병사</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>강한 전투 지속력을 가진 핵심 공격 카드입니다.</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>Peerless Soldier</x:v>
-      </x:c>
-      <x:c r="E5" t="str">
-        <x:v>A core attack card with strong combat pressure.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B6" t="str">
-        <x:v>치유사</x:v>
-      </x:c>
-      <x:c r="C6" t="str">
-        <x:v>아군의 체력을 회복시키는 지원 카드입니다.</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
-        <x:v>Healer</x:v>
-      </x:c>
-      <x:c r="E6" t="str">
-        <x:v>A support card that restores ally health.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B7" t="str">
-        <x:v>수호자</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>높은 체력으로 전열을 지키는 방어 카드입니다.</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>Guardian</x:v>
-      </x:c>
-      <x:c r="E7" t="str">
-        <x:v>A defensive card that protects the front line with high health.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B8" t="str">
-        <x:v>암살자</x:v>
-      </x:c>
-      <x:c r="C8" t="str">
-        <x:v>핵심 대상을 빠르게 제거하는 공격 카드입니다.</x:v>
-      </x:c>
-      <x:c r="D8" t="str">
-        <x:v>Assassin</x:v>
-      </x:c>
-      <x:c r="E8" t="str">
-        <x:v>An attack card that quickly removes priority targets.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B9" t="str">
-        <x:v>광전사</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>피해를 감수하고 강하게 압박하는 카드입니다.</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
-        <x:v>Berserker</x:v>
-      </x:c>
-      <x:c r="E9" t="str">
-        <x:v>A card that pressures enemies aggressively while taking risks.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B10" t="str">
-        <x:v>주술사</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
-        <x:v>특수 효과로 전투 흐름을 바꾸는 카드입니다.</x:v>
-      </x:c>
-      <x:c r="D10" t="str">
-        <x:v>Shaman</x:v>
-      </x:c>
-      <x:c r="E10" t="str">
-        <x:v>A card that changes battle flow with special effects.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B11" t="str">
-        <x:v>지휘관</x:v>
-      </x:c>
-      <x:c r="C11" t="str">
-        <x:v>아군의 전투 능력을 끌어올리는 카드입니다.</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
-        <x:v>Commander</x:v>
-      </x:c>
-      <x:c r="E11" t="str">
-        <x:v>A card that improves allied combat performance.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B12" t="str">
-        <x:v>폭탄병</x:v>
-      </x:c>
-      <x:c r="C12" t="str">
-        <x:v>폭발 피해로 적 진형을 무너뜨리는 카드입니다.</x:v>
-      </x:c>
-      <x:c r="D12" t="str">
-        <x:v>Bomber</x:v>
-      </x:c>
-      <x:c r="E12" t="str">
-        <x:v>A card that disrupts enemy formations with explosive damage.</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="55" customWidth="1"/>
+    <col min="6" max="6" width="70" customWidth="1"/>
+    <col min="7" max="7" width="86" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>cardTextKey</v>
+      </c>
+      <c r="B1" t="str">
+        <v>koreanName</v>
+      </c>
+      <c r="C1" t="str">
+        <v>koreanDescription</v>
+      </c>
+      <c r="D1" t="str">
+        <v>englishName</v>
+      </c>
+      <c r="E1" t="str">
+        <v>englishDescription</v>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>koreanLogicDescription</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>englishLogicDescription</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>int</v>
+      </c>
+      <c r="B2" t="str">
+        <v>string</v>
+      </c>
+      <c r="C2" t="str">
+        <v>string</v>
+      </c>
+      <c r="D2" t="str">
+        <v>string</v>
+      </c>
+      <c r="E2" t="str">
+        <v>string</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>일반 병사</v>
+      </c>
+      <c r="C3" t="str">
+        <v>기본 능력치를 가진 표준 카드입니다.</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Normal Soldier</v>
+      </c>
+      <c r="E3" t="str">
+        <v>A standard card with balanced stats.</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>공격 시 현재 체력만큼 피해를 주며, 공격받으면 피해 전 체력만큼 반격 피해를 받습니다.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Deals damage equal to current HP when attacking. When attacked, takes reflected damage equal to pre-hit HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="str">
+        <v>원거리 병사</v>
+      </c>
+      <c r="C4" t="str">
+        <v>후방에서 안정적으로 공격하는 카드입니다.</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Ranged Soldier</v>
+      </c>
+      <c r="E4" t="str">
+        <v>A card that attacks reliably from the back line.</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>공격 시 현재 체력만큼 피해를 주고, 공격 후 반격 피해를 받지 않습니다.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Deals damage equal to current HP when attacking and takes no reflected damage after the attack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="str">
+        <v>무쌍 병사</v>
+      </c>
+      <c r="C5" t="str">
+        <v>강한 전투 지속력을 가진 핵심 공격 카드입니다.</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Peerless Soldier</v>
+      </c>
+      <c r="E5" t="str">
+        <v>A core attack card with strong combat pressure.</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>공격/스킬 시 대상에게 현재 체력만큼 피해를 주고, 열린 인접 적 하나에게 그 피해의 50%를 추가로 줍니다. 반격 피해는 피해 전 체력의 120%입니다.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Attack/skill deals current HP damage to the target, then deals 50% of that damage to one open adjacent enemy. Reflected damage is 120% of pre-hit HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="str">
+        <v>치유사</v>
+      </c>
+      <c r="C6" t="str">
+        <v>아군의 체력을 회복시키는 지원 카드입니다.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Healer</v>
+      </c>
+      <c r="E6" t="str">
+        <v>A support card that restores ally health.</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>턴 시작마다 자신을 제외한 앞쪽 아군 최대 3장을 1 회복합니다. 공격은 현재 체력만큼 피해를 주고, 반격 피해는 피해 전 체력만큼 받습니다.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>At turn start, heals up to the first 3 allied cards other than itself by 1. Attack deals current HP damage; reflected damage equals pre-hit HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="str">
+        <v>수호자</v>
+      </c>
+      <c r="C7" t="str">
+        <v>높은 체력으로 전열을 지키는 방어 카드입니다.</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Guardian</v>
+      </c>
+      <c r="E7" t="str">
+        <v>A defensive card that protects the front line with high health.</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>공격 피해는 현재 체력의 80%(최소 1)입니다. 스킬 사용 시 이번 턴 받는 피해를 1 줄이고, 반격 피해는 피해 전 체력의 120%입니다.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Attack deals 80% of current HP as damage, minimum 1. Skill reduces incoming damage by 1 this turn. Reflected damage is 120% of pre-hit HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="str">
+        <v>암살자</v>
+      </c>
+      <c r="C8" t="str">
+        <v>핵심 대상을 빠르게 제거하는 공격 카드입니다.</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Assassin</v>
+      </c>
+      <c r="E8" t="str">
+        <v>An attack card that quickly removes priority targets.</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>스킬은 현재 체력만큼 피해를 주며, 대상 체력이 3 이하이면 피해가 2 증가합니다. 대상이 생존하면 피해 전 체력의 150%만큼 반격 피해를 받습니다.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Skill deals current HP damage and adds 2 damage if the target has 3 HP or less. If the target survives, reflected damage is 150% of pre-hit HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="str">
+        <v>광전사</v>
+      </c>
+      <c r="C9" t="str">
+        <v>피해를 감수하고 강하게 압박하는 카드입니다.</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Berserker</v>
+      </c>
+      <c r="E9" t="str">
+        <v>A card that pressures enemies aggressively while taking risks.</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>스킬은 현재 체력+2 피해를 주고 자신에게 1 피해를 줍니다. 공격 후 반격 피해를 받지 않습니다.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Skill deals current HP + 2 damage and deals 1 damage to itself. It takes no reflected damage after attacking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="str">
+        <v>주술사</v>
+      </c>
+      <c r="C10" t="str">
+        <v>특수 효과로 전투 흐름을 바꾸는 카드입니다.</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Shaman</v>
+      </c>
+      <c r="E10" t="str">
+        <v>A card that changes battle flow with special effects.</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>공격 피해는 현재 체력의 절반(최소 1)입니다. 필드에 등장하면 열린 적 전체의 체력을 2 낮추고, 스킬은 대상의 다음 공격 피해를 2 낮춥니다.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Attack deals half current HP as damage, minimum 1. On entering the field, reduces all open enemies' health by 2. Skill lowers the target's next attack damage by 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="str">
+        <v>지휘관</v>
+      </c>
+      <c r="C11" t="str">
+        <v>아군의 전투 능력을 끌어올리는 카드입니다.</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Commander</v>
+      </c>
+      <c r="E11" t="str">
+        <v>A card that improves allied combat performance.</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>필드에 등장하면 열린 아군 전체의 체력을 2 올립니다. 스킬은 대상의 다음 공격 피해를 2 올리고, 반격 피해는 피해 전 체력만큼 받습니다.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>On entering the field, adds 2 health to all open allies. Skill raises the target's next attack damage by 2. Reflected damage equals pre-hit HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="str">
+        <v>폭탄병</v>
+      </c>
+      <c r="C12" t="str">
+        <v>폭발 피해로 적 진형을 무너뜨리는 카드입니다.</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Bomber</v>
+      </c>
+      <c r="E12" t="str">
+        <v>A card that disrupts enemy formations with explosive damage.</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>스킬은 자신과 같은 진영의 열린 생존 카드 전체에게 현재 체력의 50%(최소 1) 피해를 줍니다. 사망 시 처치자에게 2 피해를 줍니다.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Skill deals 50% of current HP, minimum 1, to all open living cards on its own side. On death, deals 2 damage to the killer.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/Data/CardBattle_RuntimeCardData_IntCardType.xlsx
+++ b/Data/CardBattle_RuntimeCardData_IntCardType.xlsx
@@ -1040,13 +1040,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="str">
-        <v>일반 병사</v>
+        <v>보병</v>
       </c>
       <c r="C3" t="str">
         <v>기본 능력치를 가진 표준 카드입니다.</v>
       </c>
       <c r="D3" t="str">
-        <v>Normal Soldier</v>
+        <v>Infantry</v>
       </c>
       <c r="E3" t="str">
         <v>A standard card with balanced stats.</v>
@@ -1067,13 +1067,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="str">
-        <v>원거리 병사</v>
+        <v>궁수</v>
       </c>
       <c r="C4" t="str">
         <v>후방에서 안정적으로 공격하는 카드입니다.</v>
       </c>
       <c r="D4" t="str">
-        <v>Ranged Soldier</v>
+        <v>Archer</v>
       </c>
       <c r="E4" t="str">
         <v>A card that attacks reliably from the back line.</v>

--- a/Data/CardBattle_RuntimeCardData_IntCardType.xlsx
+++ b/Data/CardBattle_RuntimeCardData_IntCardType.xlsx
@@ -1,20 +1,26 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CardData" sheetId="1" r:id="R422426bc090e450c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DataTableGuide" sheetId="2" r:id="Re54066cba8914e59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CardTypeEnum" sheetId="3" r:id="Rb502250f1b0644c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CardTextData" sheetId="4" r:id="RCardTextData"/>
-  </x:sheets>
-</x:workbook>
+<file path=xl\featurePropertyBag\featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:numFmts count="2">
     <x:numFmt numFmtId="200" formatCode="0.00"/>
@@ -204,24 +210,7 @@
 </x:styleSheet>
 </file>
 
-<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
-<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
-  <xfpb:bag type="Checkbox"/>
-  <xfpb:bag type="XFControls">
-    <xfpb:bagId k="CellControl">0</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplement">
-    <xfpb:bagId k="XFControls">1</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <xfpb:a k="MappedFeaturePropertyBags">
-      <xfpb:bagId>2</xfpb:bagId>
-    </xfpb:a>
-  </xfpb:bag>
-</xfpb:FeaturePropertyBags>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\tables\table1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RuntimeCardDataTable" displayName="RuntimeCardDataTable" ref="A1:U12" headerRowCount="1">
   <x:tableColumns count="21">
     <x:tableColumn id="1" name="CardId"/>
@@ -250,7 +239,7 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\tables\table2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DataTableGuideTable" displayName="DataTableGuideTable" ref="A1:B10" headerRowCount="1">
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="항목"/>
@@ -260,7 +249,7 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\tables\table3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CardTypeEnumTable" displayName="CardTypeEnumTable" ref="A1:C11" headerRowCount="1">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="EnumName"/>
@@ -271,7 +260,7 @@
 </x:table>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
     <a:clrScheme name="ChatGPT">
@@ -416,7 +405,18 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CardData" sheetId="1" r:id="R422426bc090e450c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DataTableGuide" sheetId="2" r:id="Re54066cba8914e59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CardTypeEnum" sheetId="3" r:id="Rb502250f1b0644c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CardTextData" sheetId="4" r:id="RCardTextData"/>
+  </x:sheets>
+</x:workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
     <x:row r="1">
@@ -735,7 +735,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -831,7 +831,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -969,7 +969,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>공격 피해는 현재 체력의 80%(최소 1)입니다. 스킬 사용 시 이번 턴 받는 피해를 1 줄이고, 반격 피해는 피해 전 체력의 120%입니다.</t>
+          <t>공격 피해는 현재 체력의 80%(최소 1)입니다. 반격 피해는 피해 전 체력의 120%입니다.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Attack deals 80% of current HP as damage, minimum 1. Skill reduces incoming damage by 1 this turn. Reflected damage is 120% of pre-hit HP.</t>
+          <t>Attack deals 80% of current HP as damage, minimum 1. Reflected damage is 120% of pre-hit HP.</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>스킬은 현재 체력만큼 피해를 주며, 대상 체력이 3 이하이면 피해가 2 증가합니다. 대상이 생존하면 피해 전 체력의 150%만큼 반격 피해를 받습니다.</t>
+          <t>공격 시 현재 체력만큼 피해를 줍니다. 대상이 생존하면 피해 전 체력의 150%만큼 반격 피해를 받습니다.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Skill deals current HP damage and adds 2 damage if the target has 3 HP or less. If the target survives, reflected damage is 150% of pre-hit HP.</t>
+          <t>Attack deals current HP damage. If the target survives, reflected damage is 150% of pre-hit HP.</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>스킬은 현재 체력+2 피해를 주고 자신에게 1 피해를 줍니다. 공격 후 반격 피해를 받지 않습니다.</t>
+          <t>공격 시 현재 체력의 120%(최소 1) 피해를 줍니다. 반격 피해는 정상적으로 받고, 공격 후 자신에게 최대 체력의 20%(최소 1) 피해를 줍니다.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Skill deals current HP + 2 damage and deals 1 damage to itself. It takes no reflected damage after attacking.</t>
+          <t>Attack deals 120% of current HP, minimum 1. It takes reflected damage normally, then deals 20% of max HP, minimum 1, to itself after attacking.</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>공격 피해는 현재 체력의 절반(최소 1)입니다. 필드에 등장하면 열린 적 전체의 체력을 2 낮추고, 스킬은 대상의 다음 공격 피해를 2 낮춥니다.</t>
+          <t>공격 시 현재 체력만큼 피해를 주고, 반격 피해는 피해 전 체력만큼 받습니다. 필드에 등장하면 열린 적 전체의 현재 체력이 초기 체력을 초과한 만큼 모두 깎습니다.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Attack deals half current HP as damage, minimum 1. On entering the field, reduces all open enemies' health by 2. Skill lowers the target's next attack damage by 2.</t>
+          <t>Attack deals current HP damage and reflected damage equals pre-hit HP. On entering the field, removes all current HP above initial HP from all open enemies.</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>필드에 등장하면 열린 아군 전체의 체력을 2 올립니다. 스킬은 대상의 다음 공격 피해를 2 올리고, 반격 피해는 피해 전 체력만큼 받습니다.</t>
+          <t>필드에 등장하면 열린 아군 전체의 현재 체력을 2 올립니다. 반격 피해는 피해 전 체력만큼 받습니다.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>On entering the field, adds 2 health to all open allies. Skill raises the target's next attack damage by 2. Reflected damage equals pre-hit HP.</t>
+          <t>On entering the field, adds 2 current HP to all open allies. Reflected damage equals pre-hit HP.</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>스킬은 자신과 같은 진영의 열린 생존 카드 전체에게 현재 체력의 50%(최소 1) 피해를 줍니다. 사망 시 처치자에게 2 피해를 줍니다.</t>
+          <t>공격 시 선택한 적에게 현재 체력의 50%(최소 1) 피해를 주고, 나머지 공개된 적들에게 현재 체력의 30%(최소 1) 피해를 줍니다. 반격 피해를 받지 않습니다.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skill deals 50% of current HP, minimum 1, to all open living cards on its own side. On death, deals 2 damage to the killer.</t>
+          <t>Attack deals 50% of current HP, minimum 1, to the selected enemy and 30% of current HP, minimum 1, to each other open enemy. Takes no reflected damage.</t>
         </is>
       </c>
     </row>
